--- a/public/templates/import-third-parties.xlsx
+++ b/public/templates/import-third-parties.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -623,99 +623,106 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * department            -&gt; Departamento.</t>
+          <t xml:space="preserve">  * city_code             -&gt; Codigo DANE del municipio (5 digitos, ej. 11001 = Bogota).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * country_code          -&gt; Codigo pais (default CO).</t>
+          <t xml:space="preserve">  * department            -&gt; Departamento.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * tax_regime            -&gt; Regimen tributario. Ver desplegable.</t>
+          <t xml:space="preserve">  * country_code          -&gt; Codigo pais (default CO).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * is_responsible_for_iva -&gt; TRUE/FALSE (default FALSE).</t>
+          <t xml:space="preserve">  * tax_regime            -&gt; Regimen tributario. Ver desplegable.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * obligated_accounting  -&gt; TRUE/FALSE (default FALSE).</t>
+          <t xml:space="preserve">  * is_responsible_for_iva -&gt; TRUE/FALSE (default FALSE).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * default_payment_terms -&gt; Dias de plazo de pago (ej. 30).</t>
+          <t xml:space="preserve">  * obligated_accounting  -&gt; TRUE/FALSE (default FALSE).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * max_credit_amount     -&gt; Limite de credito en pesos.</t>
+          <t xml:space="preserve">  * default_payment_terms -&gt; Dias de plazo de pago (ej. 30).</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * default_currency      -&gt; Moneda: COP, USD, EUR (default COP).</t>
+          <t xml:space="preserve">  * max_credit_amount     -&gt; Limite de credito en pesos.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  * default_currency      -&gt; Moneda: COP, USD, EUR (default COP).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  * is_active             -&gt; TRUE/FALSE (default TRUE).</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="6" customHeight="1">
-      <c r="A26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="27" ht="6" customHeight="1">
+      <c r="A27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>NOTAS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * No modifiques los nombres de las columnas (fila 1).</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Si document_number ya existe para el tenant, se actualizara el registro.</t>
+          <t xml:space="preserve">  * No modifiques los nombres de las columnas (fila 1).</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Las filas en blanco se ignoran.</t>
+          <t xml:space="preserve">  * Si document_number ya existe para el tenant, se actualizara el registro.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Las filas en blanco se ignoran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  * Booleanos aceptan: TRUE / FALSE (en mayusculas).</t>
         </is>
@@ -732,7 +739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -746,15 +753,16 @@
     <col width="26" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -815,45 +823,50 @@
       </c>
       <c r="L1" s="7" t="inlineStr">
         <is>
+          <t>city_code</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
           <t>department</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>tax_regime</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>is_responsible_for_iva</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>obligated_accounting</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>default_payment_terms</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>max_credit_amount</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>default_currency</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
@@ -913,39 +926,44 @@
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
+          <t>11001</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
           <t>Cundinamarca</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
+      <c r="N2" s="8" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="O2" s="8" t="inlineStr">
         <is>
           <t>ORDINARIO</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="P2" s="8" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="P2" s="8" t="inlineStr">
+      <c r="Q2" s="8" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Q2" s="8" t="n">
+      <c r="R2" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R2" s="8" t="inlineStr"/>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="S2" s="8" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>COP</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -959,19 +977,19 @@
     <dataValidation sqref="E2:E1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
       <formula1>=listas_ref!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
+    <dataValidation sqref="O2:O1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
       <formula1>=listas_ref!$G$2:$G$5</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
+    <dataValidation sqref="T2:T1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
       <formula1>=listas_ref!$L$2:$L$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
-      <formula1>=listas_ref!$J$2:$J$3</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
       <formula1>=listas_ref!$J$2:$J$3</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
+    <dataValidation sqref="Q2:Q1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
+      <formula1>=listas_ref!$J$2:$J$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="U2:U1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor invalido" error="Selecciona de la lista (listas_ref)" type="list">
       <formula1>=listas_ref!$J$2:$J$3</formula1>
     </dataValidation>
   </dataValidations>
